--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Carahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
@@ -99,15 +99,15 @@
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
+    <t xml:space="preserve">Curarrehue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gorbea</t>
   </si>
   <si>
     <t xml:space="preserve">Toltén</t>
   </si>
   <si>
-    <t xml:space="preserve">Curarrehue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:23</t>
+    <t xml:space="preserve">2026-09-09 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -826,7 +826,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9102</v>
+        <v>9112</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
@@ -843,7 +843,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9112</v>
+        <v>9102</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
@@ -928,7 +928,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>9107</v>
+        <v>9104</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
@@ -945,7 +945,7 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9118</v>
+        <v>9107</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
@@ -962,7 +962,7 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9104</v>
+        <v>9118</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:19</t>
+    <t xml:space="preserve">2026-09-17 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
+    <t xml:space="preserve">Carahue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Padre Las Casas</t>
   </si>
   <si>
-    <t xml:space="preserve">Carahue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lumaco</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:14</t>
+    <t xml:space="preserve">2026-09-23 12:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -826,7 +826,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9112</v>
+        <v>9102</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
@@ -843,7 +843,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>9102</v>
+        <v>9112</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:43</t>
+    <t xml:space="preserve">2026-10-02 14:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:59</t>
+    <t xml:space="preserve">2026-10-05 11:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
